--- a/Thesis Forecasting/metadata/rbfnn/testing_daily_metrics.xlsx
+++ b/Thesis Forecasting/metadata/rbfnn/testing_daily_metrics.xlsx
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.346689660624237</v>
+        <v>3.346645808650762</v>
       </c>
       <c r="D6" t="n">
-        <v>1.258164583333333</v>
+        <v>1.25814662557145</v>
       </c>
       <c r="E6" t="n">
-        <v>2.20440666367487</v>
+        <v>2.204379865038043</v>
       </c>
       <c r="F6" t="n">
         <v>24</v>
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.801701911594812</v>
+        <v>3.810539021807623</v>
       </c>
       <c r="D7" t="n">
-        <v>1.943816666666667</v>
+        <v>1.949242179952438</v>
       </c>
       <c r="E7" t="n">
-        <v>3.106102839404765</v>
+        <v>3.119641977189232</v>
       </c>
       <c r="F7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.485222923468964</v>
+        <v>2.492486096313662</v>
       </c>
       <c r="D8" t="n">
-        <v>1.533775166666668</v>
+        <v>1.538186387720863</v>
       </c>
       <c r="E8" t="n">
-        <v>1.91579040272129</v>
+        <v>1.920093167736799</v>
       </c>
       <c r="F8" t="n">
         <v>24</v>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6.238484678713883</v>
+        <v>6.242072674215678</v>
       </c>
       <c r="D9" t="n">
-        <v>2.330185416666667</v>
+        <v>2.332393645762404</v>
       </c>
       <c r="E9" t="n">
-        <v>5.127563581994457</v>
+        <v>5.128600399060957</v>
       </c>
       <c r="F9" t="n">
         <v>24</v>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.287693538431969</v>
+        <v>4.286413328123815</v>
       </c>
       <c r="D11" t="n">
-        <v>2.005927083333333</v>
+        <v>2.005138180436939</v>
       </c>
       <c r="E11" t="n">
-        <v>4.233388947939797</v>
+        <v>4.233018569497202</v>
       </c>
       <c r="F11" t="n">
         <v>24</v>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.282511388908825</v>
+        <v>2.281005732376857</v>
       </c>
       <c r="D12" t="n">
-        <v>1.385599833333334</v>
+        <v>1.384809647113237</v>
       </c>
       <c r="E12" t="n">
-        <v>1.785227547200637</v>
+        <v>1.788710482697242</v>
       </c>
       <c r="F12" t="n">
         <v>24</v>
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6.327752607856922</v>
+        <v>6.326493377846738</v>
       </c>
       <c r="D13" t="n">
-        <v>3.312210583333334</v>
+        <v>3.311432628366634</v>
       </c>
       <c r="E13" t="n">
-        <v>5.899516832407818</v>
+        <v>5.899238080534694</v>
       </c>
       <c r="F13" t="n">
         <v>24</v>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.58381268761425</v>
+        <v>3.580153670350308</v>
       </c>
       <c r="D14" t="n">
-        <v>2.098235416666666</v>
+        <v>2.096079174928369</v>
       </c>
       <c r="E14" t="n">
-        <v>2.626869817962213</v>
+        <v>2.626470492287442</v>
       </c>
       <c r="F14" t="n">
         <v>24</v>
@@ -758,13 +758,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.743582457304412</v>
+        <v>3.743692305707228</v>
       </c>
       <c r="D15" t="n">
-        <v>2.212326916666667</v>
+        <v>2.212378542709752</v>
       </c>
       <c r="E15" t="n">
-        <v>2.81418907474631</v>
+        <v>2.814588457210752</v>
       </c>
       <c r="F15" t="n">
         <v>24</v>
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.388856122416025</v>
+        <v>2.388859514888232</v>
       </c>
       <c r="D16" t="n">
-        <v>1.431864416666666</v>
+        <v>1.431866959448931</v>
       </c>
       <c r="E16" t="n">
-        <v>1.785795207415965</v>
+        <v>1.785806964363966</v>
       </c>
       <c r="F16" t="n">
         <v>24</v>
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.666557369232077</v>
+        <v>2.666537521597326</v>
       </c>
       <c r="D17" t="n">
-        <v>1.583416499999999</v>
+        <v>1.583405712529422</v>
       </c>
       <c r="E17" t="n">
-        <v>1.904035135217396</v>
+        <v>1.904027344752532</v>
       </c>
       <c r="F17" t="n">
         <v>24</v>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.230951989685224</v>
+        <v>6.230932191406946</v>
       </c>
       <c r="D18" t="n">
-        <v>2.164647916666666</v>
+        <v>2.164641762293067</v>
       </c>
       <c r="E18" t="n">
-        <v>5.922517518556122</v>
+        <v>5.922488684753171</v>
       </c>
       <c r="F18" t="n">
         <v>24</v>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12.52103335979245</v>
+        <v>12.52056934144111</v>
       </c>
       <c r="D19" t="n">
-        <v>4.399779666666666</v>
+        <v>4.39963157426899</v>
       </c>
       <c r="E19" t="n">
-        <v>8.533029149792078</v>
+        <v>8.532363831938364</v>
       </c>
       <c r="F19" t="n">
         <v>24</v>
@@ -868,13 +868,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.376073149190186</v>
+        <v>2.372930760731323</v>
       </c>
       <c r="D20" t="n">
-        <v>1.436445833333333</v>
+        <v>1.434640664327207</v>
       </c>
       <c r="E20" t="n">
-        <v>1.741240622312626</v>
+        <v>1.739925424670008</v>
       </c>
       <c r="F20" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.02282370653625</v>
+        <v>3.026557444314905</v>
       </c>
       <c r="D21" t="n">
-        <v>1.782081416666667</v>
+        <v>1.784514039143146</v>
       </c>
       <c r="E21" t="n">
-        <v>2.214812350000146</v>
+        <v>2.217309412898561</v>
       </c>
       <c r="F21" t="n">
         <v>24</v>
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.358679598882821</v>
+        <v>2.360069475116451</v>
       </c>
       <c r="D22" t="n">
-        <v>1.407158333333334</v>
+        <v>1.407947595565022</v>
       </c>
       <c r="E22" t="n">
-        <v>1.72905623239722</v>
+        <v>1.730354110261405</v>
       </c>
       <c r="F22" t="n">
         <v>24</v>
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.932928973387162</v>
+        <v>2.932267583484613</v>
       </c>
       <c r="D23" t="n">
-        <v>1.726683333333333</v>
+        <v>1.726275475302649</v>
       </c>
       <c r="E23" t="n">
-        <v>1.979101285779735</v>
+        <v>1.978657054223381</v>
       </c>
       <c r="F23" t="n">
         <v>24</v>
@@ -956,13 +956,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.65743466153034</v>
+        <v>2.657411508778765</v>
       </c>
       <c r="D24" t="n">
-        <v>1.581369250000001</v>
+        <v>1.581355533481122</v>
       </c>
       <c r="E24" t="n">
-        <v>2.099261883930358</v>
+        <v>2.099254772399204</v>
       </c>
       <c r="F24" t="n">
         <v>24</v>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5.522781840148147</v>
+        <v>5.486114858085924</v>
       </c>
       <c r="D25" t="n">
-        <v>3.102585560976742</v>
+        <v>3.083705453064034</v>
       </c>
       <c r="E25" t="n">
-        <v>4.20960947119598</v>
+        <v>4.193527087847298</v>
       </c>
       <c r="F25" t="n">
         <v>24</v>
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5.116371461995633</v>
+        <v>5.134892456809052</v>
       </c>
       <c r="D26" t="n">
-        <v>2.840204333333334</v>
+        <v>2.850489868316647</v>
       </c>
       <c r="E26" t="n">
-        <v>3.841334393675458</v>
+        <v>3.857146234909275</v>
       </c>
       <c r="F26" t="n">
         <v>24</v>
@@ -1022,13 +1022,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.724145212791642</v>
+        <v>1.731802286182126</v>
       </c>
       <c r="D27" t="n">
-        <v>1.040289583323634</v>
+        <v>1.044995009437951</v>
       </c>
       <c r="E27" t="n">
-        <v>1.327049290420381</v>
+        <v>1.336514192397607</v>
       </c>
       <c r="F27" t="n">
         <v>24</v>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.428240038905686</v>
+        <v>2.412449090301715</v>
       </c>
       <c r="D28" t="n">
-        <v>1.427171000038805</v>
+        <v>1.418068674126737</v>
       </c>
       <c r="E28" t="n">
-        <v>2.143160238330085</v>
+        <v>2.12616498124572</v>
       </c>
       <c r="F28" t="n">
         <v>24</v>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.78577304976058</v>
+        <v>23.78167997112043</v>
       </c>
       <c r="D29" t="n">
-        <v>5.908973166676367</v>
+        <v>5.906668011144102</v>
       </c>
       <c r="E29" t="n">
-        <v>12.91851977647542</v>
+        <v>12.91858873367642</v>
       </c>
       <c r="F29" t="n">
         <v>24</v>
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.637561933601811</v>
+        <v>2.648422351569018</v>
       </c>
       <c r="D30" t="n">
-        <v>1.581256249999999</v>
+        <v>1.587881923790646</v>
       </c>
       <c r="E30" t="n">
-        <v>1.908924662795565</v>
+        <v>1.916326885986255</v>
       </c>
       <c r="F30" t="n">
         <v>24</v>
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.930312688783554</v>
+        <v>1.937606182030864</v>
       </c>
       <c r="D31" t="n">
-        <v>1.164925</v>
+        <v>1.169340320619754</v>
       </c>
       <c r="E31" t="n">
-        <v>1.430652090310453</v>
+        <v>1.435690604922962</v>
       </c>
       <c r="F31" t="n">
         <v>24</v>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.346480898132658</v>
+        <v>2.341423605460164</v>
       </c>
       <c r="D32" t="n">
-        <v>1.407062333333331</v>
+        <v>1.404075916246226</v>
       </c>
       <c r="E32" t="n">
-        <v>1.920471995528439</v>
+        <v>1.919303482783952</v>
       </c>
       <c r="F32" t="n">
         <v>24</v>
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.807668460915621</v>
+        <v>2.81214787920394</v>
       </c>
       <c r="D33" t="n">
-        <v>1.671337666666666</v>
+        <v>1.673997455173578</v>
       </c>
       <c r="E33" t="n">
-        <v>2.084073975460644</v>
+        <v>2.084907207747697</v>
       </c>
       <c r="F33" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2.850388818654893</v>
+        <v>2.850382894523776</v>
       </c>
       <c r="D34" t="n">
-        <v>1.7468125</v>
+        <v>1.746809275217974</v>
       </c>
       <c r="E34" t="n">
-        <v>2.093901326222974</v>
+        <v>2.09389649570433</v>
       </c>
       <c r="F34" t="n">
         <v>24</v>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2.88640759639685</v>
+        <v>2.897323134244027</v>
       </c>
       <c r="D35" t="n">
-        <v>1.745218749999998</v>
+        <v>1.75184273813559</v>
       </c>
       <c r="E35" t="n">
-        <v>2.198336166593763</v>
+        <v>2.203622038865245</v>
       </c>
       <c r="F35" t="n">
         <v>24</v>
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.93025108455261</v>
+        <v>4.928680372354694</v>
       </c>
       <c r="D36" t="n">
-        <v>3.004404191055674</v>
+        <v>3.005960746146968</v>
       </c>
       <c r="E36" t="n">
-        <v>4.099495314164387</v>
+        <v>4.117371455276438</v>
       </c>
       <c r="F36" t="n">
         <v>24</v>
@@ -1242,13 +1242,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.963014518027177</v>
+        <v>1.969643210934529</v>
       </c>
       <c r="D37" t="n">
-        <v>1.185322583333333</v>
+        <v>1.1893268615753</v>
       </c>
       <c r="E37" t="n">
-        <v>1.523160949841972</v>
+        <v>1.527022821952189</v>
       </c>
       <c r="F37" t="n">
         <v>24</v>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.513896374703995</v>
+        <v>2.518236252273203</v>
       </c>
       <c r="D38" t="n">
-        <v>1.487916833333334</v>
+        <v>1.490517861439385</v>
       </c>
       <c r="E38" t="n">
-        <v>1.728171403444694</v>
+        <v>1.730494802197273</v>
       </c>
       <c r="F38" t="n">
         <v>24</v>
@@ -1286,13 +1286,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3.167475953621071</v>
+        <v>3.167500436056742</v>
       </c>
       <c r="D39" t="n">
-        <v>1.881095833333334</v>
+        <v>1.88107046379596</v>
       </c>
       <c r="E39" t="n">
-        <v>2.173140802837757</v>
+        <v>2.173151223078284</v>
       </c>
       <c r="F39" t="n">
         <v>24</v>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.223033652726353</v>
+        <v>2.222825271389564</v>
       </c>
       <c r="D40" t="n">
-        <v>1.338106416666668</v>
+        <v>1.338114639391288</v>
       </c>
       <c r="E40" t="n">
-        <v>1.622707678872415</v>
+        <v>1.622457855247887</v>
       </c>
       <c r="F40" t="n">
         <v>24</v>
@@ -1330,13 +1330,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2.97331778443269</v>
+        <v>2.977074723958193</v>
       </c>
       <c r="D41" t="n">
-        <v>1.762443916666669</v>
+        <v>1.764645867134852</v>
       </c>
       <c r="E41" t="n">
-        <v>2.013565311548524</v>
+        <v>2.014078425970803</v>
       </c>
       <c r="F41" t="n">
         <v>24</v>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3.102430799014239</v>
+        <v>3.106824789703684</v>
       </c>
       <c r="D42" t="n">
-        <v>1.819845833333333</v>
+        <v>1.8224983312143</v>
       </c>
       <c r="E42" t="n">
-        <v>2.428801354663792</v>
+        <v>2.431352968722705</v>
       </c>
       <c r="F42" t="n">
         <v>24</v>
@@ -1374,13 +1374,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3.120344796844224</v>
+        <v>3.121051549804796</v>
       </c>
       <c r="D43" t="n">
-        <v>1.813270833333333</v>
+        <v>1.813665867789463</v>
       </c>
       <c r="E43" t="n">
-        <v>2.322442360111799</v>
+        <v>2.323079592781377</v>
       </c>
       <c r="F43" t="n">
         <v>24</v>
@@ -1396,13 +1396,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.850981223441366</v>
+        <v>2.849671284223503</v>
       </c>
       <c r="D44" t="n">
-        <v>1.648685416666668</v>
+        <v>1.647891785950027</v>
       </c>
       <c r="E44" t="n">
-        <v>2.409010406806945</v>
+        <v>2.408672991835227</v>
       </c>
       <c r="F44" t="n">
         <v>24</v>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5.261253043598814</v>
+        <v>5.283051226825986</v>
       </c>
       <c r="D45" t="n">
-        <v>2.845458355689923</v>
+        <v>2.856515026507818</v>
       </c>
       <c r="E45" t="n">
-        <v>3.478600767422048</v>
+        <v>3.4856996990152</v>
       </c>
       <c r="F45" t="n">
         <v>24</v>
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4.329005322968207</v>
+        <v>4.349593374391133</v>
       </c>
       <c r="D46" t="n">
-        <v>2.416233522783449</v>
+        <v>2.426572469437212</v>
       </c>
       <c r="E46" t="n">
-        <v>3.094884131106271</v>
+        <v>3.095371983530264</v>
       </c>
       <c r="F46" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3.277955277988897</v>
+        <v>3.273940467702122</v>
       </c>
       <c r="D47" t="n">
-        <v>1.908483166666666</v>
+        <v>1.906037355653597</v>
       </c>
       <c r="E47" t="n">
-        <v>2.538699948092002</v>
+        <v>2.53728656397433</v>
       </c>
       <c r="F47" t="n">
         <v>24</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.630060615129531</v>
+        <v>2.643266254939461</v>
       </c>
       <c r="D48" t="n">
-        <v>1.568591166666665</v>
+        <v>1.576395323815464</v>
       </c>
       <c r="E48" t="n">
-        <v>2.247574757883927</v>
+        <v>2.249930680498784</v>
       </c>
       <c r="F48" t="n">
         <v>24</v>
@@ -1506,13 +1506,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3.191600569035572</v>
+        <v>3.187166930305193</v>
       </c>
       <c r="D49" t="n">
-        <v>1.877676916666666</v>
+        <v>1.875072192335342</v>
       </c>
       <c r="E49" t="n">
-        <v>2.320095592223482</v>
+        <v>2.319170993528499</v>
       </c>
       <c r="F49" t="n">
         <v>24</v>
@@ -1528,13 +1528,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.776802944904784</v>
+        <v>2.775982582116361</v>
       </c>
       <c r="D50" t="n">
-        <v>1.662629166666665</v>
+        <v>1.662242228197677</v>
       </c>
       <c r="E50" t="n">
-        <v>1.999796001784014</v>
+        <v>1.999122190220347</v>
       </c>
       <c r="F50" t="n">
         <v>24</v>
@@ -1550,13 +1550,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3.09641190113234</v>
+        <v>3.08607347806749</v>
       </c>
       <c r="D51" t="n">
-        <v>1.803968916666666</v>
+        <v>1.797930640197705</v>
       </c>
       <c r="E51" t="n">
-        <v>2.458968536049178</v>
+        <v>2.450265952095834</v>
       </c>
       <c r="F51" t="n">
         <v>24</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.040742190975885</v>
+        <v>2.048100291175431</v>
       </c>
       <c r="D52" t="n">
-        <v>1.214070833333333</v>
+        <v>1.218470118402192</v>
       </c>
       <c r="E52" t="n">
-        <v>1.391370234022922</v>
+        <v>1.394396093605783</v>
       </c>
       <c r="F52" t="n">
         <v>24</v>
@@ -1594,13 +1594,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.437284167235511</v>
+        <v>2.456595948140254</v>
       </c>
       <c r="D53" t="n">
-        <v>1.404134916666664</v>
+        <v>1.415377929337898</v>
       </c>
       <c r="E53" t="n">
-        <v>1.829727226052057</v>
+        <v>1.841302074264009</v>
       </c>
       <c r="F53" t="n">
         <v>24</v>
@@ -1616,13 +1616,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2.007538542009724</v>
+        <v>1.999235898215175</v>
       </c>
       <c r="D54" t="n">
-        <v>1.175027083333333</v>
+        <v>1.170202451974897</v>
       </c>
       <c r="E54" t="n">
-        <v>1.486829771029902</v>
+        <v>1.483910343451508</v>
       </c>
       <c r="F54" t="n">
         <v>24</v>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.587598384165314</v>
+        <v>1.597771397967979</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9568435833333334</v>
+        <v>0.9630524358120081</v>
       </c>
       <c r="E55" t="n">
-        <v>1.292545087762061</v>
+        <v>1.30315892850595</v>
       </c>
       <c r="F55" t="n">
         <v>24</v>
@@ -1660,13 +1660,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.941696664562854</v>
+        <v>1.948922803631886</v>
       </c>
       <c r="D56" t="n">
-        <v>1.164150166666667</v>
+        <v>1.168571454425377</v>
       </c>
       <c r="E56" t="n">
-        <v>1.594520799791377</v>
+        <v>1.60110078706823</v>
       </c>
       <c r="F56" t="n">
         <v>24</v>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2.82744318427366</v>
+        <v>2.827834457589164</v>
       </c>
       <c r="D57" t="n">
-        <v>1.668433333333333</v>
+        <v>1.668673521130033</v>
       </c>
       <c r="E57" t="n">
-        <v>2.27603923683622</v>
+        <v>2.272701866415413</v>
       </c>
       <c r="F57" t="n">
         <v>24</v>
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2.995287002410278</v>
+        <v>2.989304494974177</v>
       </c>
       <c r="D58" t="n">
-        <v>1.750583333333334</v>
+        <v>1.747053027648044</v>
       </c>
       <c r="E58" t="n">
-        <v>2.27630216405541</v>
+        <v>2.26993249368831</v>
       </c>
       <c r="F58" t="n">
         <v>24</v>
@@ -1726,13 +1726,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.587647383227069</v>
+        <v>1.59499332525649</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9429732499999991</v>
+        <v>0.9473743307363932</v>
       </c>
       <c r="E59" t="n">
-        <v>1.126927089155356</v>
+        <v>1.132346502914326</v>
       </c>
       <c r="F59" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>20.66580215190605</v>
+        <v>20.66572955157817</v>
       </c>
       <c r="D60" t="n">
-        <v>6.384801083333332</v>
+        <v>6.384781270299268</v>
       </c>
       <c r="E60" t="n">
-        <v>14.87849631655597</v>
+        <v>14.87847065812394</v>
       </c>
       <c r="F60" t="n">
         <v>24</v>
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3.860727106662385</v>
+        <v>3.868014305843211</v>
       </c>
       <c r="D61" t="n">
-        <v>2.148495833333335</v>
+        <v>2.152907856372682</v>
       </c>
       <c r="E61" t="n">
-        <v>3.299579359649499</v>
+        <v>3.301713291772177</v>
       </c>
       <c r="F61" t="n">
         <v>24</v>
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.37980930778207</v>
+        <v>2.372232357163526</v>
       </c>
       <c r="D62" t="n">
-        <v>1.411885250000001</v>
+        <v>1.407498616521462</v>
       </c>
       <c r="E62" t="n">
-        <v>1.704999231663024</v>
+        <v>1.702214690503042</v>
       </c>
       <c r="F62" t="n">
         <v>24</v>
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.820185185441572</v>
+        <v>2.819502149675326</v>
       </c>
       <c r="D63" t="n">
-        <v>1.667920833333334</v>
+        <v>1.667507386280658</v>
       </c>
       <c r="E63" t="n">
-        <v>2.190103767043167</v>
+        <v>2.189908164755495</v>
       </c>
       <c r="F63" t="n">
         <v>24</v>
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2.533241964525636</v>
+        <v>2.533963316385528</v>
       </c>
       <c r="D64" t="n">
-        <v>1.4890375</v>
+        <v>1.489438159178819</v>
       </c>
       <c r="E64" t="n">
-        <v>1.874126683062451</v>
+        <v>1.874615547993987</v>
       </c>
       <c r="F64" t="n">
         <v>24</v>
@@ -1858,13 +1858,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3.585761948447789</v>
+        <v>3.574569756973101</v>
       </c>
       <c r="D65" t="n">
-        <v>2.063476916666668</v>
+        <v>2.056966407445659</v>
       </c>
       <c r="E65" t="n">
-        <v>2.676057206078532</v>
+        <v>2.665587790050941</v>
       </c>
       <c r="F65" t="n">
         <v>24</v>
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3.934779479700484</v>
+        <v>3.929178624302575</v>
       </c>
       <c r="D66" t="n">
-        <v>2.140241666453238</v>
+        <v>2.137370709520977</v>
       </c>
       <c r="E66" t="n">
-        <v>3.125384635236623</v>
+        <v>3.126738791464044</v>
       </c>
       <c r="F66" t="n">
         <v>24</v>
@@ -1902,13 +1902,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2.802532719597925</v>
+        <v>2.798764984280567</v>
       </c>
       <c r="D67" t="n">
-        <v>1.628645833333333</v>
+        <v>1.626424972748322</v>
       </c>
       <c r="E67" t="n">
-        <v>2.033822137011985</v>
+        <v>2.03359876346352</v>
       </c>
       <c r="F67" t="n">
         <v>24</v>
@@ -1924,13 +1924,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2.30461695653329</v>
+        <v>2.299912404613304</v>
       </c>
       <c r="D68" t="n">
-        <v>1.345466833333333</v>
+        <v>1.342855500026578</v>
       </c>
       <c r="E68" t="n">
-        <v>1.657775713659921</v>
+        <v>1.654704016033639</v>
       </c>
       <c r="F68" t="n">
         <v>24</v>
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4.410503946209692</v>
+        <v>4.412176358748106</v>
       </c>
       <c r="D69" t="n">
-        <v>2.528301916666666</v>
+        <v>2.529296589035631</v>
       </c>
       <c r="E69" t="n">
-        <v>3.362782485190626</v>
+        <v>3.365795874841069</v>
       </c>
       <c r="F69" t="n">
         <v>24</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2.899519687444403</v>
+        <v>2.907664848464728</v>
       </c>
       <c r="D70" t="n">
-        <v>1.680781250000003</v>
+        <v>1.685606498088006</v>
       </c>
       <c r="E70" t="n">
-        <v>2.106437278063091</v>
+        <v>2.108424538025257</v>
       </c>
       <c r="F70" t="n">
         <v>24</v>
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.357236982309999</v>
+        <v>1.356114368174966</v>
       </c>
       <c r="D71" t="n">
-        <v>0.7933041666666663</v>
+        <v>0.7926851320418212</v>
       </c>
       <c r="E71" t="n">
-        <v>1.056410031466633</v>
+        <v>1.055154854937793</v>
       </c>
       <c r="F71" t="n">
         <v>24</v>
@@ -2012,13 +2012,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3.677934919349633</v>
+        <v>3.695628748931221</v>
       </c>
       <c r="D72" t="n">
-        <v>2.11355625</v>
+        <v>2.124021001669887</v>
       </c>
       <c r="E72" t="n">
-        <v>2.855659379361883</v>
+        <v>2.876806802760462</v>
       </c>
       <c r="F72" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3.68438065976889</v>
+        <v>3.693385345165261</v>
       </c>
       <c r="D73" t="n">
-        <v>2.108516500019403</v>
+        <v>2.113729572303808</v>
       </c>
       <c r="E73" t="n">
-        <v>2.745670748032623</v>
+        <v>2.755228011829211</v>
       </c>
       <c r="F73" t="n">
         <v>24</v>
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3.294832473931487</v>
+        <v>3.287212030289195</v>
       </c>
       <c r="D74" t="n">
-        <v>1.907195833333333</v>
+        <v>1.902875497269257</v>
       </c>
       <c r="E74" t="n">
-        <v>2.410734822806731</v>
+        <v>2.406536395844006</v>
       </c>
       <c r="F74" t="n">
         <v>24</v>
@@ -2078,13 +2078,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3.105937943787014</v>
+        <v>3.102058530078054</v>
       </c>
       <c r="D75" t="n">
-        <v>1.809322750000001</v>
+        <v>1.807110800309383</v>
       </c>
       <c r="E75" t="n">
-        <v>2.331444127223118</v>
+        <v>2.32968502718125</v>
       </c>
       <c r="F75" t="n">
         <v>24</v>
@@ -2100,13 +2100,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2.878764419257461</v>
+        <v>2.878852288018568</v>
       </c>
       <c r="D76" t="n">
-        <v>1.690714416666667</v>
+        <v>1.69075255692604</v>
       </c>
       <c r="E76" t="n">
-        <v>2.101268679105117</v>
+        <v>2.101021196326068</v>
       </c>
       <c r="F76" t="n">
         <v>24</v>
@@ -2122,13 +2122,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3.303888702235818</v>
+        <v>3.287776868813554</v>
       </c>
       <c r="D77" t="n">
-        <v>1.9066</v>
+        <v>1.897072910204282</v>
       </c>
       <c r="E77" t="n">
-        <v>2.768658698549052</v>
+        <v>2.75274992629965</v>
       </c>
       <c r="F77" t="n">
         <v>24</v>
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2.764827457221596</v>
+        <v>2.729028301707055</v>
       </c>
       <c r="D78" t="n">
-        <v>1.510983337398166</v>
+        <v>1.49306619573049</v>
       </c>
       <c r="E78" t="n">
-        <v>2.155233305602815</v>
+        <v>2.151623324800981</v>
       </c>
       <c r="F78" t="n">
         <v>24</v>
@@ -2166,13 +2166,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2.391444279459634</v>
+        <v>2.367610671095841</v>
       </c>
       <c r="D79" t="n">
-        <v>1.339743728846365</v>
+        <v>1.327423202643593</v>
       </c>
       <c r="E79" t="n">
-        <v>1.737606991649765</v>
+        <v>1.71971663393962</v>
       </c>
       <c r="F79" t="n">
         <v>24</v>
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2.997352275021875</v>
+        <v>2.99744696619223</v>
       </c>
       <c r="D80" t="n">
-        <v>1.754131249999999</v>
+        <v>1.754137797779776</v>
       </c>
       <c r="E80" t="n">
-        <v>2.260386654124872</v>
+        <v>2.261109709042044</v>
       </c>
       <c r="F80" t="n">
         <v>24</v>
@@ -2210,13 +2210,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2.190785396208238</v>
+        <v>2.193129639765031</v>
       </c>
       <c r="D81" t="n">
-        <v>1.287235416666668</v>
+        <v>1.288627681154324</v>
       </c>
       <c r="E81" t="n">
-        <v>1.6636218494389</v>
+        <v>1.664128879984622</v>
       </c>
       <c r="F81" t="n">
         <v>24</v>
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3.404085252577111</v>
+        <v>3.404504300244209</v>
       </c>
       <c r="D82" t="n">
-        <v>1.985670833333332</v>
+        <v>1.986070108954856</v>
       </c>
       <c r="E82" t="n">
-        <v>2.437253985747414</v>
+        <v>2.435315795240732</v>
       </c>
       <c r="F82" t="n">
         <v>24</v>
@@ -2254,13 +2254,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3.655624840863497</v>
+        <v>3.647520162340428</v>
       </c>
       <c r="D83" t="n">
-        <v>2.11336304347826</v>
+        <v>2.108485385962349</v>
       </c>
       <c r="E83" t="n">
-        <v>3.297825962851572</v>
+        <v>3.282500437785571</v>
       </c>
       <c r="F83" t="n">
         <v>23</v>
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0.09308229511666288</v>
+        <v>0.09308229513381343</v>
       </c>
       <c r="D189" t="n">
-        <v>0.1249999999769571</v>
+        <v>0.1249999999999976</v>
       </c>
       <c r="E189" t="n">
-        <v>0.149100975284646</v>
+        <v>0.1491009752930293</v>
       </c>
       <c r="F189" t="n">
         <v>24</v>
@@ -4608,13 +4608,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>0.1230439026694097</v>
+        <v>0.1230439026531483</v>
       </c>
       <c r="D190" t="n">
-        <v>0.1648000000218275</v>
+        <v>0.1647999999999996</v>
       </c>
       <c r="E190" t="n">
-        <v>0.20205711242283</v>
+        <v>0.2020571123882225</v>
       </c>
       <c r="F190" t="n">
         <v>24</v>
@@ -4652,13 +4652,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.2742091346984115</v>
+        <v>0.2742091346259445</v>
       </c>
       <c r="D192" t="n">
-        <v>0.375629166767317</v>
+        <v>0.3756291666666662</v>
       </c>
       <c r="E192" t="n">
-        <v>1.06033976056859</v>
+        <v>1.060339760603488</v>
       </c>
       <c r="F192" t="n">
         <v>24</v>
@@ -4696,13 +4696,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.08938667610911694</v>
+        <v>0.08938667609181011</v>
       </c>
       <c r="D194" t="n">
-        <v>0.1187958333563704</v>
+        <v>0.1187958333333299</v>
       </c>
       <c r="E194" t="n">
-        <v>0.1476694859935426</v>
+        <v>0.1476694859587846</v>
       </c>
       <c r="F194" t="n">
         <v>24</v>
@@ -4856,7 +4856,7 @@
         <v>0.06839883333332963</v>
       </c>
       <c r="E201" t="n">
-        <v>0.08483073919674605</v>
+        <v>0.08483073919674664</v>
       </c>
       <c r="F201" t="n">
         <v>24</v>
@@ -8458,13 +8458,13 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>0.001334050438549693</v>
+        <v>0.001334050438547455</v>
       </c>
       <c r="D365" t="n">
-        <v>0.002117999999994661</v>
+        <v>0.002117999999991108</v>
       </c>
       <c r="E365" t="n">
-        <v>0.002117999999994661</v>
+        <v>0.002117999999991109</v>
       </c>
       <c r="F365" t="n">
         <v>24</v>
@@ -9514,13 +9514,13 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>2.784501548711069</v>
+        <v>2.784501548985074</v>
       </c>
       <c r="D413" t="n">
-        <v>0.6427639999320914</v>
+        <v>0.6427640000000004</v>
       </c>
       <c r="E413" t="n">
-        <v>0.9948521704792097</v>
+        <v>0.9948521704943566</v>
       </c>
       <c r="F413" t="n">
         <v>24</v>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>1.221593751801436</v>
+        <v>1.221593751526102</v>
       </c>
       <c r="D414" t="n">
-        <v>0.2962818334012427</v>
+        <v>0.2962818333333337</v>
       </c>
       <c r="E414" t="n">
-        <v>0.5209151557584686</v>
+        <v>0.5209151555234303</v>
       </c>
       <c r="F414" t="n">
         <v>24</v>
@@ -9558,13 +9558,13 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>7.050690850400822</v>
+        <v>7.050690850778913</v>
       </c>
       <c r="D415" t="n">
-        <v>1.352909833284827</v>
+        <v>1.352909833333333</v>
       </c>
       <c r="E415" t="n">
-        <v>2.555496981097961</v>
+        <v>2.555496981304028</v>
       </c>
       <c r="F415" t="n">
         <v>24</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>2.893846516594895</v>
+        <v>2.893846516312698</v>
       </c>
       <c r="D416" t="n">
-        <v>0.7007610000679088</v>
+        <v>0.7007609999999999</v>
       </c>
       <c r="E416" t="n">
-        <v>0.9781685101212191</v>
+        <v>0.9781685100971437</v>
       </c>
       <c r="F416" t="n">
         <v>24</v>
@@ -9602,13 +9602,13 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>0.8704062644906814</v>
+        <v>0.8704062647600547</v>
       </c>
       <c r="D417" t="n">
-        <v>0.2183818332654253</v>
+        <v>0.2183818333333343</v>
       </c>
       <c r="E417" t="n">
-        <v>0.3006140038736345</v>
+        <v>0.3006140039219741</v>
       </c>
       <c r="F417" t="n">
         <v>24</v>
@@ -9624,13 +9624,13 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>1.390959493991876</v>
+        <v>1.39095949379699</v>
       </c>
       <c r="D418" t="n">
-        <v>0.344298500048507</v>
+        <v>0.3442985000000006</v>
       </c>
       <c r="E418" t="n">
-        <v>0.4742564459748978</v>
+        <v>0.4742564458750144</v>
       </c>
       <c r="F418" t="n">
         <v>24</v>
@@ -9646,13 +9646,13 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>6.470213363497359</v>
+        <v>6.470213363865862</v>
       </c>
       <c r="D419" t="n">
-        <v>1.332444333284828</v>
+        <v>1.332444333333335</v>
       </c>
       <c r="E419" t="n">
-        <v>2.03598226318025</v>
+        <v>2.035982263217765</v>
       </c>
       <c r="F419" t="n">
         <v>24</v>
@@ -9668,13 +9668,13 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>10.88373857180549</v>
+        <v>10.88373857221352</v>
       </c>
       <c r="D420" t="n">
-        <v>1.736847333284826</v>
+        <v>1.736847333333332</v>
       </c>
       <c r="E420" t="n">
-        <v>2.922406157807591</v>
+        <v>2.922406157832502</v>
       </c>
       <c r="F420" t="n">
         <v>24</v>
@@ -9690,13 +9690,13 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>6.789532381243688</v>
+        <v>6.789532381604046</v>
       </c>
       <c r="D421" t="n">
-        <v>1.492380666598758</v>
+        <v>1.492380666666667</v>
       </c>
       <c r="E421" t="n">
-        <v>2.27296394299837</v>
+        <v>2.272963943013028</v>
       </c>
       <c r="F421" t="n">
         <v>24</v>
@@ -9712,13 +9712,13 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>3.395718591070187</v>
+        <v>3.395718590853054</v>
       </c>
       <c r="D422" t="n">
-        <v>0.7935931667151727</v>
+        <v>0.7935931666666662</v>
       </c>
       <c r="E422" t="n">
-        <v>1.103548439851757</v>
+        <v>1.103548439831256</v>
       </c>
       <c r="F422" t="n">
         <v>24</v>
@@ -9734,13 +9734,13 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>3.092016718043494</v>
+        <v>3.092016717858846</v>
       </c>
       <c r="D423" t="n">
-        <v>0.7022431667151734</v>
+        <v>0.702243166666667</v>
       </c>
       <c r="E423" t="n">
-        <v>1.020248090723753</v>
+        <v>1.020248090737738</v>
       </c>
       <c r="F423" t="n">
         <v>24</v>
@@ -9756,13 +9756,13 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>3.34410771468864</v>
+        <v>3.344107714376116</v>
       </c>
       <c r="D424" t="n">
-        <v>0.7084223334012408</v>
+        <v>0.7084223333333318</v>
       </c>
       <c r="E424" t="n">
-        <v>0.9185437126998028</v>
+        <v>0.9185437126618772</v>
       </c>
       <c r="F424" t="n">
         <v>24</v>
@@ -9778,13 +9778,13 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>5.260494762650734</v>
+        <v>5.260494762876224</v>
       </c>
       <c r="D425" t="n">
-        <v>1.156680666618158</v>
+        <v>1.156680666666664</v>
       </c>
       <c r="E425" t="n">
-        <v>1.605908518452573</v>
+        <v>1.605908518462573</v>
       </c>
       <c r="F425" t="n">
         <v>24</v>
@@ -9800,13 +9800,13 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>3.217836528326794</v>
+        <v>3.217836528551474</v>
       </c>
       <c r="D426" t="n">
-        <v>0.7456556666181605</v>
+        <v>0.7456556666666669</v>
       </c>
       <c r="E426" t="n">
-        <v>1.340931519265242</v>
+        <v>1.340931519285132</v>
       </c>
       <c r="F426" t="n">
         <v>24</v>
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>7.101871133805697</v>
+        <v>7.101871134046718</v>
       </c>
       <c r="D427" t="n">
-        <v>1.99851516661816</v>
+        <v>1.998515166666667</v>
       </c>
       <c r="E427" t="n">
-        <v>3.92122442840349</v>
+        <v>3.921224428388069</v>
       </c>
       <c r="F427" t="n">
         <v>24</v>
@@ -9844,13 +9844,13 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>1.665063739149885</v>
+        <v>1.665063739283299</v>
       </c>
       <c r="D428" t="n">
-        <v>0.5932359999514919</v>
+        <v>0.5932359999999983</v>
       </c>
       <c r="E428" t="n">
-        <v>0.7768187071163114</v>
+        <v>0.7768187071236957</v>
       </c>
       <c r="F428" t="n">
         <v>24</v>
@@ -9866,13 +9866,13 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>5.704092648677411</v>
+        <v>5.704092648554427</v>
       </c>
       <c r="D429" t="n">
-        <v>1.56310983338184</v>
+        <v>1.563109833333334</v>
       </c>
       <c r="E429" t="n">
-        <v>2.745351479183319</v>
+        <v>2.745351479219738</v>
       </c>
       <c r="F429" t="n">
         <v>24</v>
@@ -9888,13 +9888,13 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>4.57064678047533</v>
+        <v>4.570646780309891</v>
       </c>
       <c r="D430" t="n">
-        <v>1.485323500048506</v>
+        <v>1.485323499999999</v>
       </c>
       <c r="E430" t="n">
-        <v>1.965084235056591</v>
+        <v>1.965084235019115</v>
       </c>
       <c r="F430" t="n">
         <v>24</v>
@@ -9910,13 +9910,13 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>4.12146338738801</v>
+        <v>4.121463387528373</v>
       </c>
       <c r="D431" t="n">
-        <v>1.338737611062606</v>
+        <v>1.338737611111113</v>
       </c>
       <c r="E431" t="n">
-        <v>2.293376736240611</v>
+        <v>2.293376736241078</v>
       </c>
       <c r="F431" t="n">
         <v>24</v>
@@ -9932,13 +9932,13 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>3.774318096045406</v>
+        <v>3.774318096244409</v>
       </c>
       <c r="D432" t="n">
-        <v>1.383048499932092</v>
+        <v>1.383048500000001</v>
       </c>
       <c r="E432" t="n">
-        <v>1.663917565094725</v>
+        <v>1.663917565121741</v>
       </c>
       <c r="F432" t="n">
         <v>24</v>
@@ -9954,13 +9954,13 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>5.153319434015645</v>
+        <v>5.153319433822237</v>
       </c>
       <c r="D433" t="n">
-        <v>1.715689000067908</v>
+        <v>1.715688999999999</v>
       </c>
       <c r="E433" t="n">
-        <v>2.246363713433001</v>
+        <v>2.246363713405288</v>
       </c>
       <c r="F433" t="n">
         <v>24</v>
@@ -9976,13 +9976,13 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>2.846913905222738</v>
+        <v>2.846913905092509</v>
       </c>
       <c r="D434" t="n">
-        <v>1.103930666715173</v>
+        <v>1.103930666666667</v>
       </c>
       <c r="E434" t="n">
-        <v>1.4414487575782</v>
+        <v>1.441448757571354</v>
       </c>
       <c r="F434" t="n">
         <v>24</v>
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>4.206508216701513</v>
+        <v>4.206508216840035</v>
       </c>
       <c r="D435" t="n">
-        <v>1.575235999951495</v>
+        <v>1.575236000000001</v>
       </c>
       <c r="E435" t="n">
-        <v>1.961992055546469</v>
+        <v>1.961992055625439</v>
       </c>
       <c r="F435" t="n">
         <v>24</v>
@@ -10020,13 +10020,13 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>4.062877288907325</v>
+        <v>4.062877288721674</v>
       </c>
       <c r="D436" t="n">
-        <v>1.525097333401243</v>
+        <v>1.525097333333335</v>
       </c>
       <c r="E436" t="n">
-        <v>2.020516106224113</v>
+        <v>2.020516106197621</v>
       </c>
       <c r="F436" t="n">
         <v>24</v>
@@ -10042,13 +10042,13 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>3.308298248707522</v>
+        <v>3.308298248590209</v>
       </c>
       <c r="D437" t="n">
-        <v>1.274665166715174</v>
+        <v>1.274665166666668</v>
       </c>
       <c r="E437" t="n">
-        <v>1.588949560378373</v>
+        <v>1.588949560271607</v>
       </c>
       <c r="F437" t="n">
         <v>24</v>
@@ -10064,13 +10064,13 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>3.83309397020153</v>
+        <v>3.833093970031551</v>
       </c>
       <c r="D438" t="n">
-        <v>1.558255666734576</v>
+        <v>1.558255666666667</v>
       </c>
       <c r="E438" t="n">
-        <v>2.152953945638312</v>
+        <v>2.152953945622309</v>
       </c>
       <c r="F438" t="n">
         <v>24</v>
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>3.719146819765985</v>
+        <v>3.719146819947255</v>
       </c>
       <c r="D439" t="n">
-        <v>1.439918166598757</v>
+        <v>1.439918166666666</v>
       </c>
       <c r="E439" t="n">
-        <v>1.966534417874114</v>
+        <v>1.966534417942894</v>
       </c>
       <c r="F439" t="n">
         <v>24</v>
@@ -10108,13 +10108,13 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>6.048706116680924</v>
+        <v>6.048706116568098</v>
       </c>
       <c r="D440" t="n">
-        <v>2.300727666715172</v>
+        <v>2.300727666666666</v>
       </c>
       <c r="E440" t="n">
-        <v>2.983532912025673</v>
+        <v>2.98353291198047</v>
       </c>
       <c r="F440" t="n">
         <v>24</v>
@@ -10130,13 +10130,13 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>4.916633855799657</v>
+        <v>4.916633855664116</v>
       </c>
       <c r="D441" t="n">
-        <v>1.973952666715172</v>
+        <v>1.973952666666665</v>
       </c>
       <c r="E441" t="n">
-        <v>2.555037193720185</v>
+        <v>2.555037193709188</v>
       </c>
       <c r="F441" t="n">
         <v>24</v>
@@ -10152,13 +10152,13 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>3.922074321741718</v>
+        <v>3.92207432158982</v>
       </c>
       <c r="D442" t="n">
-        <v>1.666980666734575</v>
+        <v>1.666980666666666</v>
       </c>
       <c r="E442" t="n">
-        <v>2.494495341575471</v>
+        <v>2.494495341474368</v>
       </c>
       <c r="F442" t="n">
         <v>24</v>
@@ -10174,13 +10174,13 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>4.988893292244881</v>
+        <v>4.988893292369086</v>
       </c>
       <c r="D443" t="n">
-        <v>2.002360999951495</v>
+        <v>2.002361000000001</v>
       </c>
       <c r="E443" t="n">
-        <v>2.451451537201982</v>
+        <v>2.451451537226602</v>
       </c>
       <c r="F443" t="n">
         <v>24</v>
@@ -10196,13 +10196,13 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>7.479568665824492</v>
+        <v>7.479568666036522</v>
       </c>
       <c r="D444" t="n">
-        <v>2.501256833284828</v>
+        <v>2.501256833333334</v>
       </c>
       <c r="E444" t="n">
-        <v>4.193951399963966</v>
+        <v>4.193951399995076</v>
       </c>
       <c r="F444" t="n">
         <v>24</v>
@@ -10218,13 +10218,13 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>5.499728231372608</v>
+        <v>5.499728231261891</v>
       </c>
       <c r="D445" t="n">
-        <v>2.195839000048506</v>
+        <v>2.195838999999999</v>
       </c>
       <c r="E445" t="n">
-        <v>2.804528737259808</v>
+        <v>2.804528737204166</v>
       </c>
       <c r="F445" t="n">
         <v>24</v>
@@ -10240,13 +10240,13 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>2.629271202866442</v>
+        <v>2.629271203039074</v>
       </c>
       <c r="D446" t="n">
-        <v>1.081219333265425</v>
+        <v>1.081219333333334</v>
       </c>
       <c r="E446" t="n">
-        <v>1.269095700783581</v>
+        <v>1.269095700845293</v>
       </c>
       <c r="F446" t="n">
         <v>24</v>
@@ -10262,13 +10262,13 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>0.3387338793603505</v>
+        <v>0.3387338795236642</v>
       </c>
       <c r="D447" t="n">
-        <v>0.1385026665987568</v>
+        <v>0.1385026666666664</v>
       </c>
       <c r="E447" t="n">
-        <v>0.1632170872076253</v>
+        <v>0.163217087250896</v>
       </c>
       <c r="F447" t="n">
         <v>24</v>
@@ -10284,13 +10284,13 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>5.583594866572691</v>
+        <v>5.583594866744977</v>
       </c>
       <c r="D448" t="n">
-        <v>2.225518166598759</v>
+        <v>2.225518166666668</v>
       </c>
       <c r="E448" t="n">
-        <v>3.249875240178772</v>
+        <v>3.249875240198306</v>
       </c>
       <c r="F448" t="n">
         <v>24</v>
@@ -10306,13 +10306,13 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>4.295030596177372</v>
+        <v>4.295030596012395</v>
       </c>
       <c r="D449" t="n">
-        <v>1.702040166734573</v>
+        <v>1.702040166666664</v>
       </c>
       <c r="E449" t="n">
-        <v>2.140241682442448</v>
+        <v>2.140241682393367</v>
       </c>
       <c r="F449" t="n">
         <v>24</v>
@@ -10328,13 +10328,13 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>3.521792365649765</v>
+        <v>3.521792365775425</v>
       </c>
       <c r="D450" t="n">
-        <v>1.369584833284827</v>
+        <v>1.369584833333334</v>
       </c>
       <c r="E450" t="n">
-        <v>1.882312004691781</v>
+        <v>1.882312004722031</v>
       </c>
       <c r="F450" t="n">
         <v>24</v>
@@ -10350,13 +10350,13 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>5.568448582920499</v>
+        <v>5.568448582815183</v>
       </c>
       <c r="D451" t="n">
-        <v>2.20612233338184</v>
+        <v>2.206122333333334</v>
       </c>
       <c r="E451" t="n">
-        <v>2.944178970297656</v>
+        <v>2.944178970279717</v>
       </c>
       <c r="F451" t="n">
         <v>24</v>
@@ -10372,13 +10372,13 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>4.877996237655849</v>
+        <v>4.877996237843592</v>
       </c>
       <c r="D452" t="n">
-        <v>2.04747649993209</v>
+        <v>2.0474765</v>
       </c>
       <c r="E452" t="n">
-        <v>2.69394827245137</v>
+        <v>2.693948272515145</v>
       </c>
       <c r="F452" t="n">
         <v>24</v>
@@ -10394,13 +10394,13 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>5.519061892283192</v>
+        <v>5.51906189212748</v>
       </c>
       <c r="D453" t="n">
-        <v>2.213859833401239</v>
+        <v>2.213859833333331</v>
       </c>
       <c r="E453" t="n">
-        <v>2.95684210122582</v>
+        <v>2.956842101080247</v>
       </c>
       <c r="F453" t="n">
         <v>24</v>
@@ -10416,13 +10416,13 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>4.498360669110207</v>
+        <v>4.498360669289131</v>
       </c>
       <c r="D454" t="n">
-        <v>1.758868166598758</v>
+        <v>1.758868166666667</v>
       </c>
       <c r="E454" t="n">
-        <v>2.230250103569858</v>
+        <v>2.230250103640249</v>
       </c>
       <c r="F454" t="n">
         <v>24</v>
@@ -10438,13 +10438,13 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>3.320063018754102</v>
+        <v>3.320063018582278</v>
       </c>
       <c r="D455" t="n">
-        <v>1.324814000067909</v>
+        <v>1.324814</v>
       </c>
       <c r="E455" t="n">
-        <v>1.604314989078939</v>
+        <v>1.604314989074985</v>
       </c>
       <c r="F455" t="n">
         <v>24</v>
@@ -10460,13 +10460,13 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>4.048704912112658</v>
+        <v>4.048704912253221</v>
       </c>
       <c r="D456" t="n">
-        <v>1.595018166618158</v>
+        <v>1.595018166666664</v>
       </c>
       <c r="E456" t="n">
-        <v>2.223647734816318</v>
+        <v>2.223647734951288</v>
       </c>
       <c r="F456" t="n">
         <v>24</v>
@@ -10482,13 +10482,13 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>7.44438716443924</v>
+        <v>7.444387164665724</v>
       </c>
       <c r="D457" t="n">
-        <v>2.555173499951494</v>
+        <v>2.5551735</v>
       </c>
       <c r="E457" t="n">
-        <v>3.867091047621172</v>
+        <v>3.867091047611974</v>
       </c>
       <c r="F457" t="n">
         <v>24</v>
@@ -10504,13 +10504,13 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>3.7699425821705</v>
+        <v>3.769942582353066</v>
       </c>
       <c r="D458" t="n">
-        <v>1.497902666598757</v>
+        <v>1.497902666666666</v>
       </c>
       <c r="E458" t="n">
-        <v>1.851769338407612</v>
+        <v>1.851769338498723</v>
       </c>
       <c r="F458" t="n">
         <v>24</v>
@@ -10526,13 +10526,13 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>5.038526498085068</v>
+        <v>5.03852649820804</v>
       </c>
       <c r="D459" t="n">
-        <v>1.959876499951495</v>
+        <v>1.959876500000002</v>
       </c>
       <c r="E459" t="n">
-        <v>2.507803560714041</v>
+        <v>2.50780356073876</v>
       </c>
       <c r="F459" t="n">
         <v>24</v>
@@ -10548,13 +10548,13 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>4.227692959005117</v>
+        <v>4.227692959171068</v>
       </c>
       <c r="D460" t="n">
-        <v>1.764390166598755</v>
+        <v>1.764390166666664</v>
       </c>
       <c r="E460" t="n">
-        <v>2.418763339558462</v>
+        <v>2.4187633396264</v>
       </c>
       <c r="F460" t="n">
         <v>24</v>
@@ -10570,13 +10570,13 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>3.961542622955113</v>
+        <v>3.961542623072636</v>
       </c>
       <c r="D461" t="n">
-        <v>1.568160999951493</v>
+        <v>1.568160999999999</v>
       </c>
       <c r="E461" t="n">
-        <v>2.138817840967095</v>
+        <v>2.138817840951085</v>
       </c>
       <c r="F461" t="n">
         <v>24</v>
@@ -10592,13 +10592,13 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>4.427556692223509</v>
+        <v>4.427556692054328</v>
       </c>
       <c r="D462" t="n">
-        <v>1.759697333401241</v>
+        <v>1.759697333333332</v>
       </c>
       <c r="E462" t="n">
-        <v>2.284793906640727</v>
+        <v>2.284793906592889</v>
       </c>
       <c r="F462" t="n">
         <v>24</v>
@@ -10614,13 +10614,13 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>2.432232692097184</v>
+        <v>2.432232692215139</v>
       </c>
       <c r="D463" t="n">
-        <v>0.9515901666181593</v>
+        <v>0.9515901666666657</v>
       </c>
       <c r="E463" t="n">
-        <v>1.601951333208267</v>
+        <v>1.601951333203977</v>
       </c>
       <c r="F463" t="n">
         <v>24</v>
@@ -10636,13 +10636,13 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>3.436819779386366</v>
+        <v>3.436819779211818</v>
       </c>
       <c r="D464" t="n">
-        <v>1.354423500067908</v>
+        <v>1.354423499999999</v>
       </c>
       <c r="E464" t="n">
-        <v>1.752196315472641</v>
+        <v>1.752196315367466</v>
       </c>
       <c r="F464" t="n">
         <v>24</v>
@@ -10658,13 +10658,13 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>4.352273579218896</v>
+        <v>4.352273579338167</v>
       </c>
       <c r="D465" t="n">
-        <v>1.760006833284828</v>
+        <v>1.760006833333334</v>
       </c>
       <c r="E465" t="n">
-        <v>2.599185802013605</v>
+        <v>2.599185802019678</v>
       </c>
       <c r="F465" t="n">
         <v>24</v>
@@ -10680,13 +10680,13 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>1.851562420610334</v>
+        <v>1.851562420444703</v>
       </c>
       <c r="D466" t="n">
-        <v>0.7536610000679088</v>
+        <v>0.7536609999999998</v>
       </c>
       <c r="E466" t="n">
-        <v>1.140669571877866</v>
+        <v>1.140669571861487</v>
       </c>
       <c r="F466" t="n">
         <v>24</v>
@@ -10702,13 +10702,13 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>5.621825568922669</v>
+        <v>5.621825568814184</v>
       </c>
       <c r="D467" t="n">
-        <v>2.238868166715172</v>
+        <v>2.238868166666666</v>
       </c>
       <c r="E467" t="n">
-        <v>3.090625299528701</v>
+        <v>3.090625299474849</v>
       </c>
       <c r="F467" t="n">
         <v>24</v>
@@ -10724,13 +10724,13 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>4.600342500855128</v>
+        <v>4.60034250067347</v>
       </c>
       <c r="D468" t="n">
-        <v>1.75230150006791</v>
+        <v>1.752301500000001</v>
       </c>
       <c r="E468" t="n">
-        <v>2.380477880002092</v>
+        <v>2.38047787995653</v>
       </c>
       <c r="F468" t="n">
         <v>24</v>
@@ -10746,13 +10746,13 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>5.146032478475221</v>
+        <v>5.146032478306256</v>
       </c>
       <c r="D469" t="n">
-        <v>2.075155666734573</v>
+        <v>2.075155666666665</v>
       </c>
       <c r="E469" t="n">
-        <v>2.880029509348191</v>
+        <v>2.880029509322892</v>
       </c>
       <c r="F469" t="n">
         <v>24</v>
@@ -10768,13 +10768,13 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>4.061140167419315</v>
+        <v>4.061140167522715</v>
       </c>
       <c r="D470" t="n">
-        <v>1.609913999951494</v>
+        <v>1.609914000000001</v>
       </c>
       <c r="E470" t="n">
-        <v>2.130416604495717</v>
+        <v>2.130416604525353</v>
       </c>
       <c r="F470" t="n">
         <v>24</v>
@@ -10790,13 +10790,13 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>4.688111066983255</v>
+        <v>4.688111066808473</v>
       </c>
       <c r="D471" t="n">
-        <v>1.955847333401242</v>
+        <v>1.955847333333333</v>
       </c>
       <c r="E471" t="n">
-        <v>2.478717710279904</v>
+        <v>2.478717710262842</v>
       </c>
       <c r="F471" t="n">
         <v>24</v>
@@ -10812,13 +10812,13 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>4.188557162234362</v>
+        <v>4.18855716205639</v>
       </c>
       <c r="D472" t="n">
-        <v>1.609494333401243</v>
+        <v>1.609494333333334</v>
       </c>
       <c r="E472" t="n">
-        <v>2.134792048749687</v>
+        <v>2.134792048663601</v>
       </c>
       <c r="F472" t="n">
         <v>24</v>
@@ -10834,13 +10834,13 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>4.457927503730704</v>
+        <v>4.457927503561518</v>
       </c>
       <c r="D473" t="n">
-        <v>1.801365166734575</v>
+        <v>1.801365166666666</v>
       </c>
       <c r="E473" t="n">
-        <v>2.789781308506702</v>
+        <v>2.789781308463801</v>
       </c>
       <c r="F473" t="n">
         <v>24</v>
@@ -10856,13 +10856,13 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>5.936642662489503</v>
+        <v>5.936642662318042</v>
       </c>
       <c r="D474" t="n">
-        <v>2.319934833401243</v>
+        <v>2.319934833333334</v>
       </c>
       <c r="E474" t="n">
-        <v>3.439634703860198</v>
+        <v>3.439634703834213</v>
       </c>
       <c r="F474" t="n">
         <v>24</v>
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>6.129242178022021</v>
+        <v>6.129242178159522</v>
       </c>
       <c r="D475" t="n">
-        <v>2.362963999951494</v>
+        <v>2.362964000000001</v>
       </c>
       <c r="E475" t="n">
-        <v>3.208141557073832</v>
+        <v>3.208141557117453</v>
       </c>
       <c r="F475" t="n">
         <v>24</v>
@@ -10900,13 +10900,13 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>4.792193733351885</v>
+        <v>4.792193733470431</v>
       </c>
       <c r="D476" t="n">
-        <v>1.816788999951493</v>
+        <v>1.816788999999999</v>
       </c>
       <c r="E476" t="n">
-        <v>2.640373602241745</v>
+        <v>2.640373602252276</v>
       </c>
       <c r="F476" t="n">
         <v>24</v>
@@ -10922,13 +10922,13 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>3.819554729877774</v>
+        <v>3.819554729705093</v>
       </c>
       <c r="D477" t="n">
-        <v>1.50683183340124</v>
+        <v>1.506831833333331</v>
       </c>
       <c r="E477" t="n">
-        <v>2.021095923183763</v>
+        <v>2.021095923159592</v>
       </c>
       <c r="F477" t="n">
         <v>24</v>
@@ -10944,13 +10944,13 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>2.115566099783215</v>
+        <v>2.115566099617789</v>
       </c>
       <c r="D478" t="n">
-        <v>0.8948431667345748</v>
+        <v>0.8948431666666657</v>
       </c>
       <c r="E478" t="n">
-        <v>1.282632841012429</v>
+        <v>1.282632840990487</v>
       </c>
       <c r="F478" t="n">
         <v>24</v>
@@ -10966,13 +10966,13 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>6.90470779389855</v>
+        <v>6.904707793794802</v>
       </c>
       <c r="D479" t="n">
-        <v>2.822936000048506</v>
+        <v>2.822936</v>
       </c>
       <c r="E479" t="n">
-        <v>3.239139426644366</v>
+        <v>3.239139426587048</v>
       </c>
       <c r="F479" t="n">
         <v>24</v>
@@ -10988,13 +10988,13 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>2.856729801423909</v>
+        <v>2.856729801540089</v>
       </c>
       <c r="D480" t="n">
-        <v>1.134760999951491</v>
+        <v>1.134760999999998</v>
       </c>
       <c r="E480" t="n">
-        <v>1.580631867172657</v>
+        <v>1.580631867188138</v>
       </c>
       <c r="F480" t="n">
         <v>24</v>
@@ -11010,13 +11010,13 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>3.830733029260428</v>
+        <v>3.830733029098185</v>
       </c>
       <c r="D481" t="n">
-        <v>1.512014000067909</v>
+        <v>1.512014</v>
       </c>
       <c r="E481" t="n">
-        <v>2.129753623992556</v>
+        <v>2.12975362397563</v>
       </c>
       <c r="F481" t="n">
         <v>24</v>
@@ -11032,13 +11032,13 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>2.848731070584648</v>
+        <v>2.848731070706232</v>
       </c>
       <c r="D482" t="n">
-        <v>1.147784833284828</v>
+        <v>1.147784833333334</v>
       </c>
       <c r="E482" t="n">
-        <v>1.772299462058767</v>
+        <v>1.772299462060707</v>
       </c>
       <c r="F482" t="n">
         <v>24</v>
@@ -11054,13 +11054,13 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>3.528928517726463</v>
+        <v>3.52892851784529</v>
       </c>
       <c r="D483" t="n">
-        <v>1.410951499951493</v>
+        <v>1.410951499999999</v>
       </c>
       <c r="E483" t="n">
-        <v>1.991522284082916</v>
+        <v>1.991522284163716</v>
       </c>
       <c r="F483" t="n">
         <v>24</v>
@@ -11076,13 +11076,13 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>2.26595611639015</v>
+        <v>2.265956116226937</v>
       </c>
       <c r="D484" t="n">
-        <v>0.9505056667345771</v>
+        <v>0.9505056666666682</v>
       </c>
       <c r="E484" t="n">
-        <v>1.284980962850659</v>
+        <v>1.284980962726944</v>
       </c>
       <c r="F484" t="n">
         <v>24</v>
@@ -11098,13 +11098,13 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>6.859171088820064</v>
+        <v>6.859171089106297</v>
       </c>
       <c r="D485" t="n">
-        <v>2.309173499932093</v>
+        <v>2.309173500000002</v>
       </c>
       <c r="E485" t="n">
-        <v>3.844223468344773</v>
+        <v>3.844223468451811</v>
       </c>
       <c r="F485" t="n">
         <v>24</v>
@@ -11120,13 +11120,13 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>2.694519121910945</v>
+        <v>2.694519122079682</v>
       </c>
       <c r="D486" t="n">
-        <v>1.058309833265422</v>
+        <v>1.058309833333331</v>
       </c>
       <c r="E486" t="n">
-        <v>1.610373315207164</v>
+        <v>1.610373315214206</v>
       </c>
       <c r="F486" t="n">
         <v>24</v>
@@ -11142,13 +11142,13 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>3.606994004774162</v>
+        <v>3.606994004897987</v>
       </c>
       <c r="D487" t="n">
-        <v>1.551826499951493</v>
+        <v>1.551826499999999</v>
       </c>
       <c r="E487" t="n">
-        <v>2.081357149097081</v>
+        <v>2.081357149166699</v>
       </c>
       <c r="F487" t="n">
         <v>24</v>
@@ -11164,13 +11164,13 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>1.632284329627483</v>
+        <v>1.632284329776343</v>
       </c>
       <c r="D488" t="n">
-        <v>0.7440359999320915</v>
+        <v>0.7440360000000004</v>
       </c>
       <c r="E488" t="n">
-        <v>1.042746083061844</v>
+        <v>1.042746083108124</v>
       </c>
       <c r="F488" t="n">
         <v>24</v>
@@ -11186,13 +11186,13 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>2.126781833211269</v>
+        <v>2.126781833063248</v>
       </c>
       <c r="D489" t="n">
-        <v>0.8744973334012421</v>
+        <v>0.8744973333333332</v>
       </c>
       <c r="E489" t="n">
-        <v>1.343750225241125</v>
+        <v>1.343750225229375</v>
       </c>
       <c r="F489" t="n">
         <v>24</v>
@@ -11208,13 +11208,13 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>4.081367872242589</v>
+        <v>4.081367872409357</v>
       </c>
       <c r="D490" t="n">
-        <v>1.613431833265424</v>
+        <v>1.613431833333333</v>
       </c>
       <c r="E490" t="n">
-        <v>2.18891734804975</v>
+        <v>2.188917348063649</v>
       </c>
       <c r="F490" t="n">
         <v>24</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>4.399966331382673</v>
+        <v>4.399966331509087</v>
       </c>
       <c r="D491" t="n">
-        <v>1.78472766661816</v>
+        <v>1.784727666666667</v>
       </c>
       <c r="E491" t="n">
-        <v>2.169461079002424</v>
+        <v>2.169461079026848</v>
       </c>
       <c r="F491" t="n">
         <v>24</v>
@@ -11252,13 +11252,13 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>2.551568673072677</v>
+        <v>2.551568673238894</v>
       </c>
       <c r="D492" t="n">
-        <v>1.03591399993209</v>
+        <v>1.035913999999999</v>
       </c>
       <c r="E492" t="n">
-        <v>1.363815744036273</v>
+        <v>1.363815744056847</v>
       </c>
       <c r="F492" t="n">
         <v>24</v>
@@ -11274,13 +11274,13 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>4.667402308387794</v>
+        <v>4.667402308256317</v>
       </c>
       <c r="D493" t="n">
-        <v>1.947994087007137</v>
+        <v>1.947994086956522</v>
       </c>
       <c r="E493" t="n">
-        <v>2.8076658055006</v>
+        <v>2.807665805432597</v>
       </c>
       <c r="F493" t="n">
         <v>23</v>
